--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PAINEL - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PAINEL - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -516,7 +508,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -525,7 +516,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAINEL RT NXR150 2009 A 2010</t>
+          <t>PAINEL RT BROS NXR150 2009 A 2010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -533,7 +524,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -550,7 +540,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -571,11 +560,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,11 +580,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -621,11 +600,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PAINEL BRAVIC CF FAN TITAN150 BMA77038</t>
+          <t>PAINEL BRAVIC CG FAN TITAN150 BMA77038</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +620,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +640,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -680,7 +652,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PAINEL BRAVIC NXR150 2010 BMA77026</t>
+          <t>PAINEL BRAVIC BROS NXR150 2010 BMA77026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -688,7 +660,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,11 +680,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -734,11 +700,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +720,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,7 +740,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +760,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -822,7 +780,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
